--- a/SurveyQuestions/csvs/Demographics.xlsx
+++ b/SurveyQuestions/csvs/Demographics.xlsx
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Demographics!$A$1:$D$6</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="0" iterateDelta="1E-4"/>
 </workbook>
 </file>
 
@@ -48,9 +48,6 @@
     <t>What is your gender?</t>
   </si>
   <si>
-    <t>Female | Male | Other (specify) | Prefer not to say</t>
-  </si>
-  <si>
     <t>Role</t>
   </si>
   <si>
@@ -72,26 +69,17 @@
     <t>Socioeconomic Status</t>
   </si>
   <si>
-    <t xml:space="preserve">What is the highest level of education
-completed by your parents, step-parents, or
-guardians?
-Parent/Guardian 1
-Parent/Guardian 2
+    <t>How old are you?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What is the highest level of education completed by your parents, step-parents, or guardians?
 </t>
   </si>
   <si>
-    <t>1=8th grade or lower
-2=Between 9th and 12th grade (but no high school degree)
-3=High school degree
-4=Some college (but no college degree)
-9=Technical diploma or certificate
-5=Associate’s degree
-6=Bachelor’s degree
-7=Graduate degree
-8=Don’t know</t>
-  </si>
-  <si>
-    <t>How old are you?</t>
+    <t>Female | Male | Others | Prefer not to say</t>
+  </si>
+  <si>
+    <t>1=8th grade or lower 2=Between 9th and 12th grade (but no high school degree) 3=High school degree 4=Some college (but no college degree) 5=Associate’s degree 6=Bachelor’s degree 7=Graduate degree 8=Technical diploma or certificate 9=Don't know</t>
   </si>
 </sst>
 </file>
@@ -159,7 +147,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -171,6 +159,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -422,7 +413,7 @@
         <v>5</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D2" s="2"/>
     </row>
@@ -437,7 +428,7 @@
         <v>7</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
@@ -445,13 +436,13 @@
         <v>4</v>
       </c>
       <c r="B4" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="D4" s="3" t="s">
         <v>10</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
@@ -459,27 +450,27 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="D5" s="3" t="s">
         <v>13</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C6" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D6" s="4" t="s">
-        <v>17</v>
+      <c r="D6" s="5" t="s">
+        <v>18</v>
       </c>
     </row>
   </sheetData>
